--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P582"/>
+  <dimension ref="A1:P586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31878,6 +31878,222 @@
         <v>397.78</v>
       </c>
       <c r="P582" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>368.26</v>
+      </c>
+      <c r="C583" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="D583" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="E583" t="n">
+        <v>370.54</v>
+      </c>
+      <c r="F583" t="n">
+        <v>379.28</v>
+      </c>
+      <c r="G583" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="H583" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="I583" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="J583" t="n">
+        <v>362.32</v>
+      </c>
+      <c r="K583" t="n">
+        <v>361.83</v>
+      </c>
+      <c r="L583" t="n">
+        <v>367.74</v>
+      </c>
+      <c r="M583" t="n">
+        <v>367.28</v>
+      </c>
+      <c r="N583" t="n">
+        <v>368.81</v>
+      </c>
+      <c r="O583" t="n">
+        <v>397.14</v>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>367.32</v>
+      </c>
+      <c r="C584" t="n">
+        <v>372.13</v>
+      </c>
+      <c r="D584" t="n">
+        <v>366.96</v>
+      </c>
+      <c r="E584" t="n">
+        <v>370.74</v>
+      </c>
+      <c r="F584" t="n">
+        <v>380.13</v>
+      </c>
+      <c r="G584" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="H584" t="n">
+        <v>367.17</v>
+      </c>
+      <c r="I584" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="J584" t="n">
+        <v>361.7</v>
+      </c>
+      <c r="K584" t="n">
+        <v>361.8</v>
+      </c>
+      <c r="L584" t="n">
+        <v>367.69</v>
+      </c>
+      <c r="M584" t="n">
+        <v>367.61</v>
+      </c>
+      <c r="N584" t="n">
+        <v>369.4</v>
+      </c>
+      <c r="O584" t="n">
+        <v>395.95</v>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>367.25</v>
+      </c>
+      <c r="C585" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="D585" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="E585" t="n">
+        <v>370.75</v>
+      </c>
+      <c r="F585" t="n">
+        <v>380.21</v>
+      </c>
+      <c r="G585" t="n">
+        <v>373.48</v>
+      </c>
+      <c r="H585" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="I585" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="J585" t="n">
+        <v>361.77</v>
+      </c>
+      <c r="K585" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="L585" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="M585" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="N585" t="n">
+        <v>369.45</v>
+      </c>
+      <c r="O585" t="n">
+        <v>395.63</v>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>365.78</v>
+      </c>
+      <c r="C586" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="D586" t="n">
+        <v>367.32</v>
+      </c>
+      <c r="E586" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="F586" t="n">
+        <v>380.1</v>
+      </c>
+      <c r="G586" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="H586" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="I586" t="n">
+        <v>364.37</v>
+      </c>
+      <c r="J586" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="K586" t="n">
+        <v>361.71</v>
+      </c>
+      <c r="L586" t="n">
+        <v>367.58</v>
+      </c>
+      <c r="M586" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="N586" t="n">
+        <v>369.29</v>
+      </c>
+      <c r="O586" t="n">
+        <v>395.61</v>
+      </c>
+      <c r="P586" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31894,7 +32110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B656"/>
+  <dimension ref="A1:B660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38457,6 +38673,46 @@
       </c>
       <c r="B656" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -38625,28 +38881,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3006641902401586</v>
+        <v>0.2975083060039072</v>
       </c>
       <c r="J2" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K2" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1323993222273518</v>
+        <v>0.1315279405430898</v>
       </c>
       <c r="M2" t="n">
-        <v>4.488114171127292</v>
+        <v>4.472638105082146</v>
       </c>
       <c r="N2" t="n">
-        <v>35.331798817374</v>
+        <v>35.1358129644365</v>
       </c>
       <c r="O2" t="n">
-        <v>5.944055754901194</v>
+        <v>5.92754696012073</v>
       </c>
       <c r="P2" t="n">
-        <v>361.4918633504546</v>
+        <v>361.5244724082274</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38703,28 +38959,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1744925284371883</v>
+        <v>0.1710676689087238</v>
       </c>
       <c r="J3" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K3" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09799178328914515</v>
+        <v>0.09556576411331585</v>
       </c>
       <c r="M3" t="n">
-        <v>3.254223952769555</v>
+        <v>3.249562124311924</v>
       </c>
       <c r="N3" t="n">
-        <v>16.74306468268509</v>
+        <v>16.67663055359662</v>
       </c>
       <c r="O3" t="n">
-        <v>4.091829014351051</v>
+        <v>4.083703044247539</v>
       </c>
       <c r="P3" t="n">
-        <v>370.1037604333287</v>
+        <v>370.1391158824513</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38781,28 +39037,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1350672824461377</v>
+        <v>0.131329342748819</v>
       </c>
       <c r="J4" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K4" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04112375115320632</v>
+        <v>0.03943695028318206</v>
       </c>
       <c r="M4" t="n">
-        <v>4.043174336564213</v>
+        <v>4.035161994442023</v>
       </c>
       <c r="N4" t="n">
-        <v>25.37104638910347</v>
+        <v>25.25573899286496</v>
       </c>
       <c r="O4" t="n">
-        <v>5.036967975786968</v>
+        <v>5.025508829249528</v>
       </c>
       <c r="P4" t="n">
-        <v>366.149847271149</v>
+        <v>366.1884432829468</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38859,28 +39115,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1709688860527979</v>
+        <v>0.1650482616444607</v>
       </c>
       <c r="J5" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K5" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05933625129733644</v>
+        <v>0.05603043403663566</v>
       </c>
       <c r="M5" t="n">
-        <v>4.422522680602132</v>
+        <v>4.419510043538684</v>
       </c>
       <c r="N5" t="n">
-        <v>27.6386408781569</v>
+        <v>27.59115624210241</v>
       </c>
       <c r="O5" t="n">
-        <v>5.257246511069924</v>
+        <v>5.252728456916692</v>
       </c>
       <c r="P5" t="n">
-        <v>370.6076462299047</v>
+        <v>370.6687932569204</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38937,28 +39193,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1861960608102039</v>
+        <v>0.1856152720081246</v>
       </c>
       <c r="J6" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K6" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08088202984842563</v>
+        <v>0.0815122433763249</v>
       </c>
       <c r="M6" t="n">
-        <v>3.74246676466977</v>
+        <v>3.719580787433091</v>
       </c>
       <c r="N6" t="n">
-        <v>23.49786527550756</v>
+        <v>23.33952017759611</v>
       </c>
       <c r="O6" t="n">
-        <v>4.84745967239621</v>
+        <v>4.831099272173581</v>
       </c>
       <c r="P6" t="n">
-        <v>375.3626255712412</v>
+        <v>375.3686185750835</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39015,28 +39271,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2744250695622122</v>
+        <v>0.270395863790087</v>
       </c>
       <c r="J7" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K7" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1681998486252768</v>
+        <v>0.1657275954967694</v>
       </c>
       <c r="M7" t="n">
-        <v>3.580083120366865</v>
+        <v>3.575302907620411</v>
       </c>
       <c r="N7" t="n">
-        <v>22.21310026865556</v>
+        <v>22.12723369661944</v>
       </c>
       <c r="O7" t="n">
-        <v>4.713077579316465</v>
+        <v>4.703959363835899</v>
       </c>
       <c r="P7" t="n">
-        <v>368.8240904619072</v>
+        <v>368.8657000693493</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39093,28 +39349,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2439365246145078</v>
+        <v>0.2420426956238438</v>
       </c>
       <c r="J8" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K8" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1484598266295053</v>
+        <v>0.148267288238773</v>
       </c>
       <c r="M8" t="n">
-        <v>3.548332989962649</v>
+        <v>3.532548074825899</v>
       </c>
       <c r="N8" t="n">
-        <v>20.35720140470087</v>
+        <v>20.23279727914443</v>
       </c>
       <c r="O8" t="n">
-        <v>4.511895544524593</v>
+        <v>4.498088180454495</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9408868030336</v>
+        <v>361.9604452305192</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39171,28 +39427,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2893107237368382</v>
+        <v>0.283784819842173</v>
       </c>
       <c r="J9" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K9" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2019389424479796</v>
+        <v>0.1971366406414766</v>
       </c>
       <c r="M9" t="n">
-        <v>3.518094214352265</v>
+        <v>3.517147562820885</v>
       </c>
       <c r="N9" t="n">
-        <v>19.72937473948752</v>
+        <v>19.71816939960659</v>
       </c>
       <c r="O9" t="n">
-        <v>4.441776079395215</v>
+        <v>4.440514542213165</v>
       </c>
       <c r="P9" t="n">
-        <v>361.2935266728574</v>
+        <v>361.3506009345076</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39249,28 +39505,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.296119839761832</v>
+        <v>0.2882745188135073</v>
       </c>
       <c r="J10" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K10" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1987914408802293</v>
+        <v>0.1908207095361686</v>
       </c>
       <c r="M10" t="n">
-        <v>3.435878986610256</v>
+        <v>3.451568201487105</v>
       </c>
       <c r="N10" t="n">
-        <v>21.07905449155791</v>
+        <v>21.18584302894518</v>
       </c>
       <c r="O10" t="n">
-        <v>4.591193144658359</v>
+        <v>4.602808167732518</v>
       </c>
       <c r="P10" t="n">
-        <v>359.6967184587895</v>
+        <v>359.777753720067</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39327,28 +39583,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2599543645678422</v>
+        <v>0.255607786860403</v>
       </c>
       <c r="J11" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K11" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1510932752899986</v>
+        <v>0.1482529612336485</v>
       </c>
       <c r="M11" t="n">
-        <v>3.599195486780949</v>
+        <v>3.593979789968629</v>
       </c>
       <c r="N11" t="n">
-        <v>22.64525846575017</v>
+        <v>22.56676992826866</v>
       </c>
       <c r="O11" t="n">
-        <v>4.75870344377018</v>
+        <v>4.750449444870313</v>
       </c>
       <c r="P11" t="n">
-        <v>358.227711154569</v>
+        <v>358.2726020539146</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39405,28 +39661,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3248829032312837</v>
+        <v>0.3199252328472493</v>
       </c>
       <c r="J12" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K12" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1889717925119375</v>
+        <v>0.1859787969510097</v>
       </c>
       <c r="M12" t="n">
-        <v>3.952152818703795</v>
+        <v>3.949541940294004</v>
       </c>
       <c r="N12" t="n">
-        <v>27.0184796989838</v>
+        <v>26.93290865384392</v>
       </c>
       <c r="O12" t="n">
-        <v>5.197930328408011</v>
+        <v>5.189692539432748</v>
       </c>
       <c r="P12" t="n">
-        <v>362.7846864952929</v>
+        <v>362.8358888923671</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39483,28 +39739,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3345215662625316</v>
+        <v>0.3315086085560096</v>
       </c>
       <c r="J13" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K13" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2089849524901378</v>
+        <v>0.2081981302961863</v>
       </c>
       <c r="M13" t="n">
-        <v>3.976568541435269</v>
+        <v>3.964741102363114</v>
       </c>
       <c r="N13" t="n">
-        <v>25.26307364143458</v>
+        <v>25.12715417711594</v>
       </c>
       <c r="O13" t="n">
-        <v>5.026238518159936</v>
+        <v>5.012699290513639</v>
       </c>
       <c r="P13" t="n">
-        <v>360.8994336366023</v>
+        <v>360.9305479392287</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39561,28 +39817,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2358748714715147</v>
+        <v>0.2343949955353475</v>
       </c>
       <c r="J14" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K14" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09468867863534181</v>
+        <v>0.09485286199340681</v>
       </c>
       <c r="M14" t="n">
-        <v>4.32323134464439</v>
+        <v>4.301672413208588</v>
       </c>
       <c r="N14" t="n">
-        <v>31.72717945414474</v>
+        <v>31.5195057448643</v>
       </c>
       <c r="O14" t="n">
-        <v>5.632688474799999</v>
+        <v>5.614223521099271</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0289672157896</v>
+        <v>364.0442479452842</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39639,28 +39895,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08135981958504573</v>
+        <v>0.07626619146692781</v>
       </c>
       <c r="J15" t="n">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="K15" t="n">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007971625482793399</v>
+        <v>0.007100046091897738</v>
       </c>
       <c r="M15" t="n">
-        <v>5.385894452459564</v>
+        <v>5.374212061662892</v>
       </c>
       <c r="N15" t="n">
-        <v>48.87242537081966</v>
+        <v>48.64413726739266</v>
       </c>
       <c r="O15" t="n">
-        <v>6.990881587526688</v>
+        <v>6.974534914056467</v>
       </c>
       <c r="P15" t="n">
-        <v>397.8249676082985</v>
+        <v>397.8777978445284</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -39698,7 +39954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P582"/>
+  <dimension ref="A1:P586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87417,6 +87673,334 @@
         </is>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>-34.82956844300769,173.41111711527668</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>-34.83026533524099,173.4108853973246</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>-34.830976910197904,173.41087155318004</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>-34.83167672894361,173.41112435868098</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>-34.832315294702035,173.41152941751008</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>-34.832930023078696,173.41197138119253</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>-34.83344390263859,173.41259720908744</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>-34.83390101573813,173.41329583697066</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>-34.83425468179823,173.4140847480521</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>-34.83448057146277,173.41493733720628</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>-34.83459898533142,173.41582455643962</t>
+        </is>
+      </c>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>-34.83471131138933,173.41671031703646</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>-34.834799231483956,173.41759005509047</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>-34.83437963064789,173.41837918130622</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>-34.82956581454231,173.41110734225583</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>-34.830264719318286,173.41087942909684</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>-34.8309756363484,173.41088160571445</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>-34.83167618873758,173.41112644549102</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>-34.83231165547372,173.41153759874103</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>-34.83292765962518,173.4119745396159</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>-34.83344131119921,173.41259975785331</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>-34.833903310998465,173.41329410041828</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>-34.83425986315362,173.41408220076886</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>-34.834480832352256,173.41493725041713</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>-34.8345994282423,173.4158244541067</t>
+        </is>
+      </c>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>-34.83470836505271,173.41671082350481</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>-34.83479391838374,173.4175897185868</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>-34.83439005311762,173.418382278924</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>-34.8295656188055,173.41110661447772</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>-34.83026468572249,173.41087910355714</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>-34.83097525282365,173.41088463228388</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>-34.83167616172727,173.41112654983152</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>-34.83231131295808,173.41153836873923</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>-34.83292523557023,173.41197777902437</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>-34.83344012053786,173.41260092890784</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>-34.83390101573813,173.41329583697066</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>-34.83425927816187,173.41408248836538</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>-34.834478136494276,173.41493814723847</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>-34.83459871958489,173.41582461783935</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>-34.83470747222342,173.41671097698003</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>-34.83479346812101,173.41758969006955</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>-34.83439285579854,173.41838311189701</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-34.82956150833138,173.4110913311379</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>-34.83026422657991,173.4108746545147</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>-34.83097514324513,173.41088549701803</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-34.83167697203633,173.41112341961647</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>-34.832311783917085,173.41153730999173</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>-34.83292735661833,173.41197494454198</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>-34.833443342327364,173.41259776017196</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>-34.83390621832819,173.4132919007851</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>-34.83426922302127,173.41407759922413</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>-34.8344816150207,173.4149369900496</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>-34.83460040264625,173.41582422897432</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>-34.83470747222342,173.41671097698003</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>-34.834794908961754,173.41758978132478</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>-34.8343930309661,173.41838316395786</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P586"/>
+  <dimension ref="A1:P590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32094,6 +32094,222 @@
         <v>395.61</v>
       </c>
       <c r="P586" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>367.05</v>
+      </c>
+      <c r="C587" t="n">
+        <v>371.91</v>
+      </c>
+      <c r="D587" t="n">
+        <v>367.44</v>
+      </c>
+      <c r="E587" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="F587" t="n">
+        <v>379.99</v>
+      </c>
+      <c r="G587" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="H587" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="I587" t="n">
+        <v>364.91</v>
+      </c>
+      <c r="J587" t="n">
+        <v>360.92</v>
+      </c>
+      <c r="K587" t="n">
+        <v>362.16</v>
+      </c>
+      <c r="L587" t="n">
+        <v>368.05</v>
+      </c>
+      <c r="M587" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="N587" t="n">
+        <v>369.87</v>
+      </c>
+      <c r="O587" t="n">
+        <v>397.05</v>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="C588" t="n">
+        <v>372.27</v>
+      </c>
+      <c r="D588" t="n">
+        <v>368.13</v>
+      </c>
+      <c r="E588" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="F588" t="n">
+        <v>380.22</v>
+      </c>
+      <c r="G588" t="n">
+        <v>373.63</v>
+      </c>
+      <c r="H588" t="n">
+        <v>367.49</v>
+      </c>
+      <c r="I588" t="n">
+        <v>365.35</v>
+      </c>
+      <c r="J588" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="K588" t="n">
+        <v>362.37</v>
+      </c>
+      <c r="L588" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="M588" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="N588" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="O588" t="n">
+        <v>398.27</v>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>367.94</v>
+      </c>
+      <c r="C589" t="n">
+        <v>372.07</v>
+      </c>
+      <c r="D589" t="n">
+        <v>367.97</v>
+      </c>
+      <c r="E589" t="n">
+        <v>370.98</v>
+      </c>
+      <c r="F589" t="n">
+        <v>378.15</v>
+      </c>
+      <c r="G589" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="H589" t="n">
+        <v>367.37</v>
+      </c>
+      <c r="I589" t="n">
+        <v>365.03</v>
+      </c>
+      <c r="J589" t="n">
+        <v>361.18</v>
+      </c>
+      <c r="K589" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="L589" t="n">
+        <v>368.58</v>
+      </c>
+      <c r="M589" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="N589" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="O589" t="n">
+        <v>398.92</v>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>368.02</v>
+      </c>
+      <c r="C590" t="n">
+        <v>371.93</v>
+      </c>
+      <c r="D590" t="n">
+        <v>368.15</v>
+      </c>
+      <c r="E590" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="F590" t="n">
+        <v>378.47</v>
+      </c>
+      <c r="G590" t="n">
+        <v>374.21</v>
+      </c>
+      <c r="H590" t="n">
+        <v>367.44</v>
+      </c>
+      <c r="I590" t="n">
+        <v>365.07</v>
+      </c>
+      <c r="J590" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="K590" t="n">
+        <v>362.17</v>
+      </c>
+      <c r="L590" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="M590" t="n">
+        <v>369.16</v>
+      </c>
+      <c r="N590" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="O590" t="n">
+        <v>399.45</v>
+      </c>
+      <c r="P590" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32110,7 +32326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B660"/>
+  <dimension ref="A1:B665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38713,6 +38929,56 @@
       </c>
       <c r="B660" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -38881,28 +39147,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2975083060039072</v>
+        <v>0.2953315493311731</v>
       </c>
       <c r="J2" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K2" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1315279405430898</v>
+        <v>0.1314491024268989</v>
       </c>
       <c r="M2" t="n">
-        <v>4.472638105082146</v>
+        <v>4.452613425378384</v>
       </c>
       <c r="N2" t="n">
-        <v>35.1358129644365</v>
+        <v>34.91842330188732</v>
       </c>
       <c r="O2" t="n">
-        <v>5.92754696012073</v>
+        <v>5.909181271706539</v>
       </c>
       <c r="P2" t="n">
-        <v>361.5244724082274</v>
+        <v>361.5470401674257</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38959,28 +39225,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1710676689087238</v>
+        <v>0.1676123474365011</v>
       </c>
       <c r="J3" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K3" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09556576411331585</v>
+        <v>0.09307218557614549</v>
       </c>
       <c r="M3" t="n">
-        <v>3.249562124311924</v>
+        <v>3.245053715457535</v>
       </c>
       <c r="N3" t="n">
-        <v>16.67663055359662</v>
+        <v>16.61259612314705</v>
       </c>
       <c r="O3" t="n">
-        <v>4.083703044247539</v>
+        <v>4.075855262781917</v>
       </c>
       <c r="P3" t="n">
-        <v>370.1391158824513</v>
+        <v>370.1749210566174</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39037,28 +39303,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.131329342748819</v>
+        <v>0.1290203218323439</v>
       </c>
       <c r="J4" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K4" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03943695028318206</v>
+        <v>0.03862052045897735</v>
       </c>
       <c r="M4" t="n">
-        <v>4.035161994442023</v>
+        <v>4.019711493767211</v>
       </c>
       <c r="N4" t="n">
-        <v>25.25573899286496</v>
+        <v>25.1067360648935</v>
       </c>
       <c r="O4" t="n">
-        <v>5.025508829249528</v>
+        <v>5.010662238157098</v>
       </c>
       <c r="P4" t="n">
-        <v>366.1884432829468</v>
+        <v>366.2123822907405</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39115,28 +39381,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1650482616444607</v>
+        <v>0.1597575341984351</v>
       </c>
       <c r="J5" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K5" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05603043403663566</v>
+        <v>0.05320351327675554</v>
       </c>
       <c r="M5" t="n">
-        <v>4.419510043538684</v>
+        <v>4.413711414584272</v>
       </c>
       <c r="N5" t="n">
-        <v>27.59115624210241</v>
+        <v>27.5192322150132</v>
       </c>
       <c r="O5" t="n">
-        <v>5.252728456916692</v>
+        <v>5.24587764011068</v>
       </c>
       <c r="P5" t="n">
-        <v>370.6687932569204</v>
+        <v>370.7236499217273</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39193,28 +39459,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1856152720081246</v>
+        <v>0.1841120640782431</v>
       </c>
       <c r="J6" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K6" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0815122433763249</v>
+        <v>0.08133995157243679</v>
       </c>
       <c r="M6" t="n">
-        <v>3.719580787433091</v>
+        <v>3.701189856498837</v>
       </c>
       <c r="N6" t="n">
-        <v>23.33952017759611</v>
+        <v>23.19597882193885</v>
       </c>
       <c r="O6" t="n">
-        <v>4.831099272173581</v>
+        <v>4.816220387600515</v>
       </c>
       <c r="P6" t="n">
-        <v>375.3686185750835</v>
+        <v>375.3842162412517</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39271,28 +39537,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.270395863790087</v>
+        <v>0.2672919109342599</v>
       </c>
       <c r="J7" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K7" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1657275954967694</v>
+        <v>0.1643033710803325</v>
       </c>
       <c r="M7" t="n">
-        <v>3.575302907620411</v>
+        <v>3.56615448309929</v>
       </c>
       <c r="N7" t="n">
-        <v>22.12723369661944</v>
+        <v>22.01765677690865</v>
       </c>
       <c r="O7" t="n">
-        <v>4.703959363835899</v>
+        <v>4.692297601059491</v>
       </c>
       <c r="P7" t="n">
-        <v>368.8657000693493</v>
+        <v>368.8978787033066</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39349,28 +39615,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2420426956238438</v>
+        <v>0.2406127927392357</v>
       </c>
       <c r="J8" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K8" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L8" t="n">
-        <v>0.148267288238773</v>
+        <v>0.148562063131942</v>
       </c>
       <c r="M8" t="n">
-        <v>3.532548074825899</v>
+        <v>3.514859555015807</v>
       </c>
       <c r="N8" t="n">
-        <v>20.23279727914443</v>
+        <v>20.10387577929967</v>
       </c>
       <c r="O8" t="n">
-        <v>4.498088180454495</v>
+        <v>4.483734579488361</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9604452305192</v>
+        <v>361.9752708254117</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39427,28 +39693,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.283784819842173</v>
+        <v>0.2787856232697768</v>
       </c>
       <c r="J9" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K9" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1971366406414766</v>
+        <v>0.1930239527955298</v>
       </c>
       <c r="M9" t="n">
-        <v>3.517147562820885</v>
+        <v>3.514044398240276</v>
       </c>
       <c r="N9" t="n">
-        <v>19.71816939960659</v>
+        <v>19.68735970357007</v>
       </c>
       <c r="O9" t="n">
-        <v>4.440514542213165</v>
+        <v>4.437044027679923</v>
       </c>
       <c r="P9" t="n">
-        <v>361.3506009345076</v>
+        <v>361.4024352598942</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39505,28 +39771,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2882745188135073</v>
+        <v>0.2802644576910009</v>
       </c>
       <c r="J10" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K10" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1908207095361686</v>
+        <v>0.1825838406902934</v>
       </c>
       <c r="M10" t="n">
-        <v>3.451568201487105</v>
+        <v>3.468713886845482</v>
       </c>
       <c r="N10" t="n">
-        <v>21.18584302894518</v>
+        <v>21.30660333666595</v>
       </c>
       <c r="O10" t="n">
-        <v>4.602808167732518</v>
+        <v>4.615907639529407</v>
       </c>
       <c r="P10" t="n">
-        <v>359.777753720067</v>
+        <v>359.8608047204355</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39583,28 +39849,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.255607786860403</v>
+        <v>0.2518520151555979</v>
       </c>
       <c r="J11" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K11" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1482529612336485</v>
+        <v>0.1460453874317021</v>
       </c>
       <c r="M11" t="n">
-        <v>3.593979789968629</v>
+        <v>3.586152896769679</v>
       </c>
       <c r="N11" t="n">
-        <v>22.56676992826866</v>
+        <v>22.47165679313315</v>
       </c>
       <c r="O11" t="n">
-        <v>4.750449444870313</v>
+        <v>4.740427912449798</v>
       </c>
       <c r="P11" t="n">
-        <v>358.2726020539146</v>
+        <v>358.3115440777551</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39661,28 +39927,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3199252328472493</v>
+        <v>0.3161449127903513</v>
       </c>
       <c r="J12" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K12" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1859787969510097</v>
+        <v>0.1842609337768594</v>
       </c>
       <c r="M12" t="n">
-        <v>3.949541940294004</v>
+        <v>3.941165739356749</v>
       </c>
       <c r="N12" t="n">
-        <v>26.93290865384392</v>
+        <v>26.80943607160788</v>
       </c>
       <c r="O12" t="n">
-        <v>5.189692539432748</v>
+        <v>5.177782930136014</v>
       </c>
       <c r="P12" t="n">
-        <v>362.8358888923671</v>
+        <v>362.8750821127925</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39739,28 +40005,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3315086085560096</v>
+        <v>0.3301077869100456</v>
       </c>
       <c r="J13" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K13" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2081981302961863</v>
+        <v>0.2091532518711247</v>
       </c>
       <c r="M13" t="n">
-        <v>3.964741102363114</v>
+        <v>3.944865567468744</v>
       </c>
       <c r="N13" t="n">
-        <v>25.12715417711594</v>
+        <v>24.96528564250636</v>
       </c>
       <c r="O13" t="n">
-        <v>5.012699290513639</v>
+        <v>4.996527358326617</v>
       </c>
       <c r="P13" t="n">
-        <v>360.9305479392287</v>
+        <v>360.9450695159425</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39817,28 +40083,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2343949955353475</v>
+        <v>0.2342149331213058</v>
       </c>
       <c r="J14" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K14" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09485286199340681</v>
+        <v>0.09597925282179731</v>
       </c>
       <c r="M14" t="n">
-        <v>4.301672413208588</v>
+        <v>4.273989927099244</v>
       </c>
       <c r="N14" t="n">
-        <v>31.5195057448643</v>
+        <v>31.30599310659433</v>
       </c>
       <c r="O14" t="n">
-        <v>5.614223521099271</v>
+        <v>5.595175878075177</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0442479452842</v>
+        <v>364.0461139426436</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39895,28 +40161,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07626619146692781</v>
+        <v>0.07432723951601049</v>
       </c>
       <c r="J15" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="K15" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007100046091897738</v>
+        <v>0.006841884290036515</v>
       </c>
       <c r="M15" t="n">
-        <v>5.374212061662892</v>
+        <v>5.347293597042574</v>
       </c>
       <c r="N15" t="n">
-        <v>48.64413726739266</v>
+        <v>48.33406928757409</v>
       </c>
       <c r="O15" t="n">
-        <v>6.974534914056467</v>
+        <v>6.952270800794089</v>
       </c>
       <c r="P15" t="n">
-        <v>397.8777978445284</v>
+        <v>397.8979731359488</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -39954,7 +40220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P586"/>
+  <dimension ref="A1:P590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88001,6 +88267,334 @@
         </is>
       </c>
     </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-34.82956505955744,173.41110453511166</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>-34.83026447294912,173.41087704180578</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-34.83097497887736,173.4108867941192</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-34.83167613471697,173.41112665417202</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-34.832312254876065,173.41153625124426</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>-34.832927174814195,173.4119751874976</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>-34.83344089096578,173.41260017116667</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>-34.833902086859624,173.41329502657953</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>-34.83426638163289,173.41407899612176</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>-34.83447770167846,173.41493829188707</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>-34.83459623928392,173.4158251909036</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>-34.83470238309653,173.4167118517889</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>-34.83478968591409,173.41758945052456</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>-34.834380418901915,173.4183794155798</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-34.829568918368345,173.41111888273795</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>-34.83026487609863,173.41088094828208</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-34.83097403376236,173.41089425245082</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>-34.83167494626357,173.41113124515394</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>-34.83231127014363,173.411538464989</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>-34.8329243265496,173.41197899380245</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>-34.8334390699543,173.41260196219122</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>-34.83389872047778,173.41329757352295</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>-34.834261450988315,173.41408142014973</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>-34.83447587545208,173.41493889941117</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>-34.83459172159287,173.41582623469904</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>-34.83469675827205,173.41671281868278</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>-34.83478419270877,173.41758910261404</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>-34.83436973368075,173.41837623987155</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-34.829567548211045,173.41111378829078</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-34.8302646521267,173.4108787780175</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-34.83097425291949,173.41089252298264</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>-34.831675540490295,173.411128949663</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>-34.832320132734125,173.41151854128424</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>-34.832922447906924,173.4119815043438</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>-34.833439910421156,173.4126011355645</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>-34.83390116875549,173.41329572120048</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>-34.834264208806474,173.4140800643375</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>-34.834477266862656,173.41493843653566</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>-34.834591544428505,173.41582627563218</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>-34.83469747253547,173.41671269590262</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>-34.8347869843377,173.41758927942104</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>-34.83436404073501,173.41837454789618</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-34.82956777191021,173.41111462003727</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-34.83026449534632,173.41087725883222</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-34.83097400636771,173.41089446863435</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-34.8316756485315,173.411128532301</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>-34.83231876267203,173.4115216212775</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>-34.83292081166971,173.41198369094423</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>-34.83343942014883,173.41260161776344</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>-34.833900862720775,173.4132959527408</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>-34.834261785269305,173.41408125580887</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>-34.834477614715304,173.4149383208168</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>-34.83458906412754,173.41582684869633</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>-34.834694526198845,173.4167132023708</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>-34.8347844628664,173.4175891197244</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>-34.8343593987946,173.41837316828565</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0026/nzd0026.xlsx
+++ b/data/nzd0026/nzd0026.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P590"/>
+  <dimension ref="A1:P592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32310,6 +32310,114 @@
         <v>399.45</v>
       </c>
       <c r="P590" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>368.46</v>
+      </c>
+      <c r="C591" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="D591" t="n">
+        <v>367.81</v>
+      </c>
+      <c r="E591" t="n">
+        <v>370.94</v>
+      </c>
+      <c r="F591" t="n">
+        <v>378.25</v>
+      </c>
+      <c r="G591" t="n">
+        <v>374.28</v>
+      </c>
+      <c r="H591" t="n">
+        <v>367.26</v>
+      </c>
+      <c r="I591" t="n">
+        <v>365.24</v>
+      </c>
+      <c r="J591" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="K591" t="n">
+        <v>362.22</v>
+      </c>
+      <c r="L591" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="M591" t="n">
+        <v>369.22</v>
+      </c>
+      <c r="N591" t="n">
+        <v>370.23</v>
+      </c>
+      <c r="O591" t="n">
+        <v>399.11</v>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>369.27</v>
+      </c>
+      <c r="C592" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="D592" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="E592" t="n">
+        <v>371.34</v>
+      </c>
+      <c r="F592" t="n">
+        <v>378.4</v>
+      </c>
+      <c r="G592" t="n">
+        <v>374.31</v>
+      </c>
+      <c r="H592" t="n">
+        <v>367.14</v>
+      </c>
+      <c r="I592" t="n">
+        <v>365.19</v>
+      </c>
+      <c r="J592" t="n">
+        <v>361.28</v>
+      </c>
+      <c r="K592" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="L592" t="n">
+        <v>368.67</v>
+      </c>
+      <c r="M592" t="n">
+        <v>369.36</v>
+      </c>
+      <c r="N592" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="O592" t="n">
+        <v>398.73</v>
+      </c>
+      <c r="P592" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32326,7 +32434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B665"/>
+  <dimension ref="A1:B668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38979,6 +39087,36 @@
       </c>
       <c r="B665" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>0.79</v>
       </c>
     </row>
   </sheetData>
@@ -39147,28 +39285,28 @@
         <v>0.0504</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2953315493311731</v>
+        <v>0.294888100165394</v>
       </c>
       <c r="J2" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K2" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1314491024268989</v>
+        <v>0.1319301333815655</v>
       </c>
       <c r="M2" t="n">
-        <v>4.452613425378384</v>
+        <v>4.43963064988725</v>
       </c>
       <c r="N2" t="n">
-        <v>34.91842330188732</v>
+        <v>34.80242946855063</v>
       </c>
       <c r="O2" t="n">
-        <v>5.909181271706539</v>
+        <v>5.899358394651967</v>
       </c>
       <c r="P2" t="n">
-        <v>361.5470401674257</v>
+        <v>361.55165477673</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39225,28 +39363,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1676123474365011</v>
+        <v>0.1658419875256597</v>
       </c>
       <c r="J3" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K3" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09307218557614549</v>
+        <v>0.09176791916925886</v>
       </c>
       <c r="M3" t="n">
-        <v>3.245053715457535</v>
+        <v>3.243175953573984</v>
       </c>
       <c r="N3" t="n">
-        <v>16.61259612314705</v>
+        <v>16.58252020638407</v>
       </c>
       <c r="O3" t="n">
-        <v>4.075855262781917</v>
+        <v>4.072164069187791</v>
       </c>
       <c r="P3" t="n">
-        <v>370.1749210566174</v>
+        <v>370.1933462562454</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39303,28 +39441,28 @@
         <v>0.0741</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1290203218323439</v>
+        <v>0.1279409502928008</v>
       </c>
       <c r="J4" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K4" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03862052045897735</v>
+        <v>0.03825385114200985</v>
       </c>
       <c r="M4" t="n">
-        <v>4.019711493767211</v>
+        <v>4.011666825020318</v>
       </c>
       <c r="N4" t="n">
-        <v>25.1067360648935</v>
+        <v>25.03161234242711</v>
       </c>
       <c r="O4" t="n">
-        <v>5.010662238157098</v>
+        <v>5.003160235533848</v>
       </c>
       <c r="P4" t="n">
-        <v>366.2123822907405</v>
+        <v>366.2236216104937</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39381,28 +39519,28 @@
         <v>0.1329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1597575341984351</v>
+        <v>0.1572728089029038</v>
       </c>
       <c r="J5" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K5" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05320351327675554</v>
+        <v>0.05191115515252964</v>
       </c>
       <c r="M5" t="n">
-        <v>4.413711414584272</v>
+        <v>4.409997082289059</v>
       </c>
       <c r="N5" t="n">
-        <v>27.5192322150132</v>
+        <v>27.47767725252918</v>
       </c>
       <c r="O5" t="n">
-        <v>5.24587764011068</v>
+        <v>5.24191541829217</v>
       </c>
       <c r="P5" t="n">
-        <v>370.7236499217273</v>
+        <v>370.7495253530211</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39459,28 +39597,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1841120640782431</v>
+        <v>0.182808057127418</v>
       </c>
       <c r="J6" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K6" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08133995157243679</v>
+        <v>0.0807772144837885</v>
       </c>
       <c r="M6" t="n">
-        <v>3.701189856498837</v>
+        <v>3.694557944084191</v>
       </c>
       <c r="N6" t="n">
-        <v>23.19597882193885</v>
+        <v>23.13166861011234</v>
       </c>
       <c r="O6" t="n">
-        <v>4.816220387600515</v>
+        <v>4.809539334501002</v>
       </c>
       <c r="P6" t="n">
-        <v>375.3842162412517</v>
+        <v>375.3977961665448</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39537,28 +39675,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2672919109342599</v>
+        <v>0.2661109346086786</v>
       </c>
       <c r="J7" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K7" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1643033710803325</v>
+        <v>0.1640137104491306</v>
       </c>
       <c r="M7" t="n">
-        <v>3.56615448309929</v>
+        <v>3.559861991658344</v>
       </c>
       <c r="N7" t="n">
-        <v>22.01765677690865</v>
+        <v>21.95476685144817</v>
       </c>
       <c r="O7" t="n">
-        <v>4.692297601059491</v>
+        <v>4.685591408931018</v>
       </c>
       <c r="P7" t="n">
-        <v>368.8978787033066</v>
+        <v>368.9101779310919</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39615,28 +39753,28 @@
         <v>0.1248</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2406127927392357</v>
+        <v>0.2397822287257216</v>
       </c>
       <c r="J8" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K8" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.148562063131942</v>
+        <v>0.1485710834734403</v>
       </c>
       <c r="M8" t="n">
-        <v>3.514859555015807</v>
+        <v>3.506575841863576</v>
       </c>
       <c r="N8" t="n">
-        <v>20.10387577929967</v>
+        <v>20.04160406290695</v>
       </c>
       <c r="O8" t="n">
-        <v>4.483734579488361</v>
+        <v>4.476785014148764</v>
       </c>
       <c r="P8" t="n">
-        <v>361.9752708254117</v>
+        <v>361.9839213990404</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39693,28 +39831,28 @@
         <v>0.1462</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2787856232697768</v>
+        <v>0.27640601527406</v>
       </c>
       <c r="J9" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K9" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1930239527955298</v>
+        <v>0.1911196637110151</v>
       </c>
       <c r="M9" t="n">
-        <v>3.514044398240276</v>
+        <v>3.512032600858014</v>
       </c>
       <c r="N9" t="n">
-        <v>19.68735970357007</v>
+        <v>19.66791276348048</v>
       </c>
       <c r="O9" t="n">
-        <v>4.437044027679923</v>
+        <v>4.434852056549405</v>
       </c>
       <c r="P9" t="n">
-        <v>361.4024352598942</v>
+        <v>361.4272180641076</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39771,28 +39909,28 @@
         <v>0.1677</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2802644576910009</v>
+        <v>0.2764184038006488</v>
       </c>
       <c r="J10" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K10" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1825838406902934</v>
+        <v>0.1787133542407841</v>
       </c>
       <c r="M10" t="n">
-        <v>3.468713886845482</v>
+        <v>3.476908969500273</v>
       </c>
       <c r="N10" t="n">
-        <v>21.30660333666595</v>
+        <v>21.35777723135133</v>
       </c>
       <c r="O10" t="n">
-        <v>4.615907639529407</v>
+        <v>4.621447525543412</v>
       </c>
       <c r="P10" t="n">
-        <v>359.8608047204355</v>
+        <v>359.9008607392769</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39849,28 +39987,28 @@
         <v>0.1168</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2518520151555979</v>
+        <v>0.2500201690094475</v>
       </c>
       <c r="J11" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K11" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1460453874317021</v>
+        <v>0.1449793964994545</v>
       </c>
       <c r="M11" t="n">
-        <v>3.586152896769679</v>
+        <v>3.582038973774448</v>
       </c>
       <c r="N11" t="n">
-        <v>22.47165679313315</v>
+        <v>22.42357063714211</v>
       </c>
       <c r="O11" t="n">
-        <v>4.740427912449798</v>
+        <v>4.735353274798208</v>
       </c>
       <c r="P11" t="n">
-        <v>358.3115440777551</v>
+        <v>358.3306216309286</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39927,28 +40065,28 @@
         <v>0.1118</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3161449127903513</v>
+        <v>0.3144388645053957</v>
       </c>
       <c r="J12" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K12" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1842609337768594</v>
+        <v>0.1835921154119866</v>
       </c>
       <c r="M12" t="n">
-        <v>3.941165739356749</v>
+        <v>3.93612838123917</v>
       </c>
       <c r="N12" t="n">
-        <v>26.80943607160788</v>
+        <v>26.74299176948857</v>
       </c>
       <c r="O12" t="n">
-        <v>5.177782930136014</v>
+        <v>5.171362660797304</v>
       </c>
       <c r="P12" t="n">
-        <v>362.8750821127925</v>
+        <v>362.8928507782413</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40005,28 +40143,28 @@
         <v>0.07439999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3301077869100456</v>
+        <v>0.3297194022750815</v>
       </c>
       <c r="J13" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K13" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2091532518711247</v>
+        <v>0.2099597714804342</v>
       </c>
       <c r="M13" t="n">
-        <v>3.944865567468744</v>
+        <v>3.933444419892475</v>
       </c>
       <c r="N13" t="n">
-        <v>24.96528564250636</v>
+        <v>24.88207014055214</v>
       </c>
       <c r="O13" t="n">
-        <v>4.996527358326617</v>
+        <v>4.98819307370436</v>
       </c>
       <c r="P13" t="n">
-        <v>360.9450695159425</v>
+        <v>360.9491137977428</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -40083,28 +40221,28 @@
         <v>0.0788</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2342149331213058</v>
+        <v>0.2341941249312345</v>
       </c>
       <c r="J14" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K14" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L14" t="n">
-        <v>0.09597925282179731</v>
+        <v>0.09659662125476742</v>
       </c>
       <c r="M14" t="n">
-        <v>4.273989927099244</v>
+        <v>4.259970344917589</v>
       </c>
       <c r="N14" t="n">
-        <v>31.30599310659433</v>
+        <v>31.20011209013186</v>
       </c>
       <c r="O14" t="n">
-        <v>5.595175878075177</v>
+        <v>5.585706051174897</v>
       </c>
       <c r="P14" t="n">
-        <v>364.0461139426436</v>
+        <v>364.0463294284657</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -40161,28 +40299,28 @@
         <v>0.0274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07432723951601049</v>
+        <v>0.07369121641333401</v>
       </c>
       <c r="J15" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K15" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006841884290036515</v>
+        <v>0.00677447809438525</v>
       </c>
       <c r="M15" t="n">
-        <v>5.347293597042574</v>
+        <v>5.332292212914036</v>
       </c>
       <c r="N15" t="n">
-        <v>48.33406928757409</v>
+        <v>48.17368966454501</v>
       </c>
       <c r="O15" t="n">
-        <v>6.952270800794089</v>
+        <v>6.940726883010526</v>
       </c>
       <c r="P15" t="n">
-        <v>397.8979731359488</v>
+        <v>397.9046256121209</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -40220,7 +40358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P590"/>
+  <dimension ref="A1:P592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88595,6 +88733,170 @@
         </is>
       </c>
     </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:21+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-34.829569002255525,173.4111191946429</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-34.83026433856592,173.410875739647</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>-34.83097447207661,173.41089079351443</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>-34.8316756485315,173.411128532301</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>-34.832319704589736,173.41151950378213</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>-34.83292038746006,173.41198425784066</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>-34.83344068084908,173.41260037782337</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>-34.833899562073235,173.41329693678713</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>-34.834261367418065,173.41408146123496</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>-34.834477179899494,173.41493846546538</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>-34.83458906412754,173.41582684869633</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>-34.834693990501265,173.41671329445592</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>-34.83478644402241,173.41758924520033</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>-34.83436237664316,173.41837405331881</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-34.82957126720895,173.41112761607639</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>-34.830264663325295,173.4108788865307</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>-34.83097392418379,173.4108951171849</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-34.83167456811926,173.4111327059209</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-34.832319062373124,173.411520947529</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>-34.83292020565592,173.41198450079622</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>-34.83344152131592,173.41259955119662</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>-34.83389994461664,173.41329664736173</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>-34.83426337310401,173.4140804751897</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>-34.834476571157374,173.41493866797344</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>-34.834590747188926,173.4158264598314</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>-34.83469274054028,173.41671350932117</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>-34.83478392255113,173.4175890855037</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>-34.83436570482684,173.41837504247354</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
